--- a/Data/27/testDataNetherland1.xlsx
+++ b/Data/27/testDataNetherland1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEB7C9E-C9BF-410E-AC20-514EC5C73C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AF9A71-3C96-4576-AA7B-E1C235A8F9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -352,12 +352,6 @@
   </si>
   <si>
     <t>40</t>
-  </si>
-  <si>
-    <t>10699525</t>
-  </si>
-  <si>
-    <t>Passed</t>
   </si>
   <si>
     <t>701 Store Management (Vulam Syhohu (8701689))</t>
@@ -1267,12 +1261,8 @@
       </c>
     </row>
     <row r="2" spans="1:66" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13">
-        <v>10699524</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>109</v>
-      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="14"/>
       <c r="D2" s="15" t="s">
         <v>64</v>
       </c>
@@ -1299,7 +1289,7 @@
       </c>
       <c r="L2" s="19">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="M2" s="20" t="s">
         <v>72</v>
@@ -1348,11 +1338,11 @@
       </c>
       <c r="AB2" s="23">
         <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AC2" s="28">
         <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AD2" s="29" t="s">
         <v>84</v>
@@ -1365,7 +1355,7 @@
       </c>
       <c r="AG2" s="31">
         <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AH2" s="23">
         <v>44986</v>
@@ -1419,7 +1409,7 @@
         <v>97</v>
       </c>
       <c r="AY2" s="37">
-        <v>100000027</v>
+        <v>100000030</v>
       </c>
       <c r="AZ2" t="s">
         <v>98</v>
@@ -1468,26 +1458,22 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="15" t="s">
         <v>108</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>65</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>67</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I3" s="18" t="s">
         <v>69</v>
@@ -1500,7 +1486,7 @@
       </c>
       <c r="L3" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="M3" s="20" t="s">
         <v>72</v>
@@ -1542,18 +1528,18 @@
         <v>81</v>
       </c>
       <c r="Z3" s="25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AA3" s="27" t="s">
         <v>83</v>
       </c>
       <c r="AB3" s="23">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AD3" s="29" t="s">
         <v>84</v>
@@ -1566,25 +1552,25 @@
       </c>
       <c r="AG3" s="31">
         <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AH3" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AI3" s="18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AJ3" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK3" s="32" t="s">
         <v>88</v>
       </c>
       <c r="AL3" s="33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AM3" s="32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AN3" s="20" t="s">
         <v>91</v>
@@ -1608,7 +1594,7 @@
         <v>94</v>
       </c>
       <c r="AU3" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AV3" s="37">
         <v>251</v>
@@ -1620,7 +1606,7 @@
         <v>97</v>
       </c>
       <c r="AY3" s="37">
-        <v>100000028</v>
+        <v>100000031</v>
       </c>
       <c r="AZ3" t="s">
         <v>98</v>
@@ -1659,7 +1645,7 @@
         <v>105</v>
       </c>
       <c r="BL3" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="BM3" t="s">
         <v>107</v>

--- a/Data/27/testDataNetherland1.xlsx
+++ b/Data/27/testDataNetherland1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AF9A71-3C96-4576-AA7B-E1C235A8F9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFDEBED-F46B-4B1A-B9B8-DA1614F5DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -228,13 +228,13 @@
     <t>Mevr</t>
   </si>
   <si>
-    <t>Aubrey</t>
+    <t>Pink</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>Waters</t>
+    <t>Sanford</t>
   </si>
   <si>
     <t>071 025 8087</t>
@@ -357,10 +357,10 @@
     <t>701 Store Management (Vulam Syhohu (8701689))</t>
   </si>
   <si>
-    <t>Federico</t>
-  </si>
-  <si>
-    <t>Schroeder</t>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Emmerich</t>
   </si>
   <si>
     <t>Full-time( FT. )</t>
@@ -369,7 +369,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 36795961</t>
+    <t>Auto 71847621</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>NL Management</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
 </sst>
 </file>
@@ -489,7 +492,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1261,8 +1264,12 @@
       </c>
     </row>
     <row r="2" spans="1:66" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="13">
+        <v>10699772</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="D2" s="15" t="s">
         <v>64</v>
       </c>
@@ -1289,7 +1296,7 @@
       </c>
       <c r="L2" s="19">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="M2" s="20" t="s">
         <v>72</v>
@@ -1338,11 +1345,11 @@
       </c>
       <c r="AB2" s="23">
         <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="AC2" s="28">
         <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="AD2" s="29" t="s">
         <v>84</v>
@@ -1355,7 +1362,7 @@
       </c>
       <c r="AG2" s="31">
         <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="AH2" s="23">
         <v>44986</v>
@@ -1409,7 +1416,7 @@
         <v>97</v>
       </c>
       <c r="AY2" s="37">
-        <v>100000030</v>
+        <v>100000038</v>
       </c>
       <c r="AZ2" t="s">
         <v>98</v>
@@ -1458,8 +1465,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
+      <c r="B3" s="13">
+        <v>10699774</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="D3" s="15" t="s">
         <v>108</v>
       </c>
@@ -1486,7 +1497,7 @@
       </c>
       <c r="L3" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="M3" s="20" t="s">
         <v>72</v>
@@ -1535,11 +1546,11 @@
       </c>
       <c r="AB3" s="23">
         <f t="shared" ca="1" si="1"/>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="AD3" s="29" t="s">
         <v>84</v>
@@ -1552,7 +1563,7 @@
       </c>
       <c r="AG3" s="31">
         <f t="shared" ca="1" si="3"/>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="AH3" s="26" t="s">
         <v>84</v>
@@ -1606,7 +1617,7 @@
         <v>97</v>
       </c>
       <c r="AY3" s="37">
-        <v>100000031</v>
+        <v>100000039</v>
       </c>
       <c r="AZ3" t="s">
         <v>98</v>
